--- a/DateBase/orders/Dang Nguyen 195_2026-10-23.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-23.xlsx
@@ -1353,6 +1353,9 @@
       <c r="C111" t="str">
         <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F111" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1411,7 +1414,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0991010125156173681061025759786551055105305555510555315131253455101510655510551086105510108561010651051266101055510105510151553151010101010202015202155105100</v>
+        <v>09910101251561736810610257597865510551053055555105553151312534551015106555105510861055101085610106510512661010555101055101515531510101010102020152021551051010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-23.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-23.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L116"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1357,9 +1357,52 @@
         <v>10</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>4</v>
+      </c>
+      <c r="C112" t="str">
+        <v>636_干花大叶白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F112" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F113" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="C114" t="str">
+        <v>633_干花安娜深红_undefined_undefined_1stem</v>
+      </c>
+      <c r="F114" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="C115" t="str">
+        <v>635_干花安娜白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F115" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="C116" t="str">
+        <v>635_干花安娜白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F116" t="str">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L116"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1414,7 +1457,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>09910101251561736810610257597865510551053055555105553151312534551015106555105510861055101085610106510512661010555101055101515531510101010102020152021551051010</v>
+        <v>099101012515617368106102575978655105510530555551055531513125345510151065551055108610551010856101065105126610105551010551015155315101010101020201520215510510102030302020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-23.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-23.xlsx
@@ -1459,6 +1459,9 @@
       <c r="G2" t="str">
         <v>099101012515617368106102575978655105510530555551055531513125345510151065551055108610551010856101065105126610105551010551015155315101010101020201520215510510102030302020</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
